--- a/01_pigments/output/stat_results/Appendix S6_dunn_pairwise_pvalues_perpigpersubgenus.xlsx
+++ b/01_pigments/output/stat_results/Appendix S6_dunn_pairwise_pvalues_perpigpersubgenus.xlsx
@@ -55,6 +55,35 @@
     <sheet name="Ipomoea_nil__Neo.Car" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdlg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,7 +409,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.340500870589088</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0000000000904404480888503</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0000000000841782885850671</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0432400837061483</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0040259460654635</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0000000000959593573374276</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.875254248814641</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.483671962125111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000000145526493299983</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.043409352166641</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.107777318395141</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.51983679393183</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000000340457266540149</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.000836669538343427</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.257255836392256</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -390,7 +539,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.637475700487029</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0000000034365579659837</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0000000025992980460499</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0737445711155824</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.017891064059465</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00000000405419013034429</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.956682965562829</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.737006645872995</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00000178678650689112</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0847955919911312</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.783246491909788</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.784665342130704</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00000000000379031367234034</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0249842743667671</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.784679903276592</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -400,7 +669,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.393408725747249</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.45869632874168</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.647140893442737</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.417610148470617</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00380313038418901</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00537224703927553</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.359899940540569</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00255464561632588</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00219543828361042</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.703424805275527</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -410,7 +770,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.670454084103004</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0966691344430551</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.244747958156314</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.254752603430798</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.264286639654327</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00343426041781709</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -420,7 +846,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0497141809896535</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.433756100439143</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00446128361775933</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -430,7 +901,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00183254828479937</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.000589973746239732</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375160551264065</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -440,7 +956,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.47889461555461</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0304184066548863</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.165791654451493</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.577603941137814</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.950041154984135</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.539120283813789</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.497877159860066</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.872652119218568</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.555442988804866</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.929777720084246</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0325932844729908</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00013636710488084</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000000154576135301743</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.032601490633104</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.00393229482302178</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -450,7 +1086,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.603073475670878</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.739598552509219</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.61132229015024</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.276059823831184</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00549715605439809</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0184406857838925</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.150052762957698</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00216289326652419</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00500147458896928</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.570643641397634</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -460,7 +1187,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.236073917147975</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.107697473264883</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00259673526427861</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -470,7 +1242,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000061064899739836</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0315505124110822</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.197064116176655</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -480,7 +1297,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0471812991324176</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0496978693924491</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.000000380664177839879</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00171169219372044</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.045357776329993</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00000188895824489785</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0992208973509727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.988699363154865</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000458592016784789</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0768994730187182</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0000033066189172331</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00489695603691748</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0000000000000000000640929717139689</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.652695394812283</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0478032955067275</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -490,7 +1427,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.278827946643064</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.338623836248693</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.711895848762079</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.619192407488044</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0050368192364743</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00513566138344463</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.474567944840535</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00348859025336186</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00208698170331065</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.703424805275527</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -500,7 +1528,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7297258344298</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.962127821995882</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.566455267940208</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0965573232442933</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.126062953538609</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01024435321012</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0893767856289727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.077308669824412</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00712063596652692</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -510,7 +1629,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.18830713373074</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.132854955731054</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00232416056720667</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -520,7 +1684,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00183254828479937</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.000589973746239732</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375160551264065</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -530,7 +1739,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.175461786275755</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00430283531608485</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.131707176785913</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.631420891934607</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.642414770642963</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.192816240297187</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.609078165701417</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0971640951966075</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00425439501905914</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.449562784297509</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.00475820776418218</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0000000921789513524789</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000000000000577944286084918</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0254644144094924</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0935115860579994</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -540,7 +1869,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.272071078104325</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.433909910439383</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44380250652407</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.458558025767657</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00143372652970475</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00600808080946397</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.43164554525934</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00134479668568877</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00389041375984172</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.82109758355196</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -550,7 +1970,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.465392388124266</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.213422133228286</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0887568546909738</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0737656993465763</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.268480024019536</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00081675120800108</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -560,7 +2046,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.111813566011998</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.280036699500344</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00495808014281309</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -570,7 +2101,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000107420459830106</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.108437488118365</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0952626999934866</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -580,7 +2156,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0980783112050614</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.000000000862176164091776</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.000000241053830126224</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0373311312817527</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.000962242837882792</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.000000000645915197344249</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0130448523276909</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0000390951996066888</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0000000000000017028628177643</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.928632964001985</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.13800632239578</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.782584586972914</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00000000156582039220326</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0012971859235951</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0000499283809138801</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -590,7 +2286,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0665636600476621</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.608075423479944</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0456020774297938</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.365434868538024</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.13855190450134</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.429649131488402</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.550393251100484</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.000186024917268174</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.121988152937228</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0128441576351136</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -600,7 +2387,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0236551669686452</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.594524708806545</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0381967693197175</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -610,7 +2442,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.299297687570213</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.97658787492219</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.336734343282167</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0124726953973856</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.366894456344947</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0150300003235214</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -620,7 +2518,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00339739922145817</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.210406453095371</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0605759048459149</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -630,7 +2573,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000221554418997196</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.107307655503288</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.127102725337023</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -640,7 +2628,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.925540217639394</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0000165883957097351</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00000108867528941027</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0624317796155602</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0512228658035552</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00000284949376343225</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.317819727302973</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.338182002731962</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0224279831106487</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0191422554076806</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0508839547367848</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0338432872989706</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00449621067159874</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.00176968948803209</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.636073892261081</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -650,7 +2758,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0322160923260889</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.402865263176732</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.114485036465765</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -660,7 +2813,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.109870386840536</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.132467694919935</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.459986364338323</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.548190075604705</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0601614676011757</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.109263425170098</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.429773655492799</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.454165384512563</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.669077967282471</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.282597782026129</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.597209905719125</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.067476687106707</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.132473103830215</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.476240301304007</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.542204503265616</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -670,7 +2943,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.591971231073544</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.54451629230193</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.855408634823123</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.868841732204928</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.189837734629413</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.098507991981398</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.540705885347911</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.06444709568264</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0303552827889238</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.570732626030008</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -680,7 +3044,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.807748114787248</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.749711499584466</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.754127720868843</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0343377589069074</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.103151727241754</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.010476162285391</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -690,7 +3120,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0412113585254153</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0346289686715621</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -700,7 +3175,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0000952270880880817</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00620612442810805</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.497623973175608</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -710,7 +3230,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00209223003314254</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00047865405006809</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.333308666791511</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -720,7 +3285,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0586456592296809</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00000153111094834705</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00141409185552373</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.114303558897948</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00329622576999782</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00000178715007831808</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0152145902153585</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00001558284134388</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00000000000507879685249739</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.704723668620424</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.258363974306513</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00018806003557495</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000000000002707788642929</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.321339044473549</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0754711918563744</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -730,7 +3415,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.398297568510583</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.490838304965445</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.621201193057878</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.500498581425842</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0168734404208929</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0286565775016742</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.122631370685594</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.000216594039024178</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.000184174932969173</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.145886148128536</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -740,7 +3516,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.259484564160249</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.945406534737361</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.285302742143792</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00869434722977252</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.268480024019536</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00885928089101806</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -750,7 +3592,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0258506143913123</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.71878808092626</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00917058838742165</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -760,7 +3647,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000312702507131172</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00694336834372455</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.628573620495042</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -770,7 +3702,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.397897487284043</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0348090441322552</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.15833281288439</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.00000206149838355201</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0000000200949271204308</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0000000000686359978844681</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.330873037228787</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0755572898206803</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00334524303406572</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.000409213466562394</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.172918526637561</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.496895480810878</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.372777708015679</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.00000000132761446010551</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0227738035484413</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -780,7 +3832,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0116731670712508</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00021359204694688</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0000591780358532372</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.144897946004541</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0433907009129017</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.027647450196774</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.055870753008775</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -790,7 +3933,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0371894392604305</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0305464157095015</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.547461426869625</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -800,7 +3988,127 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.91182269295352</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.000037062172402459</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0000087920460947991</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.276482919917443</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.200543281893851</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0000452309537226269</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.85411183639662</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.854037355943328</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00021852581023643</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.41533136481013</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.967026072056255</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.962955594837062</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000000148634296159666</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.243839457453454</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.86209820107734</v>
+      </c>
+      <c r="G7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -810,7 +4118,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.428015382102817</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.433909910439383</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.739209655128595</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.437766875335283</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00574156311714297</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00513566138344463</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.340617681418055</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00145748199062417</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00291379604538318</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.625926482055622</v>
+      </c>
+      <c r="F6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -820,7 +4219,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.491839294368689</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.071451823672431</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.330595207396265</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.308207109549428</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.190089394261598</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00343426041781709</v>
+      </c>
+      <c r="E5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -830,7 +4295,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0497141809896535</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.433756100439143</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00446128361775933</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -840,7 +4350,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.00122140459630476</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.00108762113291565</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.518939744878948</v>
+      </c>
+      <c r="D4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
